--- a/artfynd/A 28269-2026 artfynd.xlsx
+++ b/artfynd/A 28269-2026 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>135624688</v>
       </c>
       <c r="B3" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>135624785</v>
       </c>
       <c r="B4" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>135624805</v>
       </c>
       <c r="B5" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>135624828</v>
       </c>
       <c r="B6" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 28269-2026 artfynd.xlsx
+++ b/artfynd/A 28269-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135624714</v>
       </c>
       <c r="B2" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>135624688</v>
       </c>
       <c r="B3" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>135624785</v>
       </c>
       <c r="B4" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>135624805</v>
       </c>
       <c r="B5" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>135624828</v>
       </c>
       <c r="B6" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 28269-2026 artfynd.xlsx
+++ b/artfynd/A 28269-2026 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>135624688</v>
       </c>
       <c r="B3" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>135624785</v>
       </c>
       <c r="B4" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>135624805</v>
       </c>
       <c r="B5" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>135624828</v>
       </c>
       <c r="B6" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 28269-2026 artfynd.xlsx
+++ b/artfynd/A 28269-2026 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>135624688</v>
       </c>
       <c r="B3" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>135624785</v>
       </c>
       <c r="B4" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>135624805</v>
       </c>
       <c r="B5" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>135624828</v>
       </c>
       <c r="B6" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 28269-2026 artfynd.xlsx
+++ b/artfynd/A 28269-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135624714</v>
       </c>
       <c r="B2" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>135624688</v>
       </c>
       <c r="B3" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>135624785</v>
       </c>
       <c r="B4" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>135624805</v>
       </c>
       <c r="B5" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>135624828</v>
       </c>
       <c r="B6" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
